--- a/data/trans_dic/IP25-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP25-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,15 +519,12 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que ven la televisión todos o casi todos los días</t>
+          <t>Menores que ven la televisión todos o casi todos los días (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -537,23 +535,20 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -575,47 +570,32 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -631,9 +611,6 @@
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -663,47 +640,32 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>59,04%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
           <t>59,06%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -716,62 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>43,14; 58,83</t>
+          <t>42,98; 58,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,97; 62,72</t>
+          <t>49,56; 63,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48,67; 62,07</t>
+          <t>49,04; 62,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,74</t>
+          <t>38,74; 52,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,27; 53,19</t>
+          <t>54,45; 67,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,09; 67,67</t>
+          <t>55,74; 69,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,4; 69,16</t>
+          <t>42,73; 53,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,64</t>
+          <t>54,08; 63,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>42,77; 53,29</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>54,39; 63,92</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>54,13; 63,8</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,85</t>
+          <t>54,35; 63,79</t>
         </is>
       </c>
     </row>
@@ -803,47 +750,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>97,91%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
           <t>97,26%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -856,62 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>95,3; 98,62</t>
+          <t>95,65; 98,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>94,51; 98,18</t>
+          <t>94,76; 98,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95,39; 99,15</t>
+          <t>95,35; 99,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>93,29; 97,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>92,92; 97,24</t>
+          <t>97,38; 99,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>97,26; 99,75</t>
+          <t>94,75; 98,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,87; 98,39</t>
+          <t>95,05; 97,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,69</t>
+          <t>96,66; 98,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>95,03; 97,6</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>96,76; 98,81</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>95,85; 98,32</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,36</t>
+          <t>95,87; 98,3</t>
         </is>
       </c>
     </row>
@@ -943,47 +860,32 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>98,17%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
           <t>97,87%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -996,62 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>95,12; 99,5</t>
+          <t>95,19; 99,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>95,99; 99,56</t>
+          <t>95,84; 99,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>94,21; 98,7</t>
+          <t>94,2; 98,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,82</t>
+          <t>91,36; 97,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91,45; 97,59</t>
+          <t>95,26; 99,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>94,52; 99,41</t>
+          <t>96,37; 99,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>96,67; 99,67</t>
+          <t>94,52; 98,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>96,52; 99,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>94,73; 98,21</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>96,39; 99,13</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>96,24; 98,92</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,4</t>
+          <t>96,28; 98,91</t>
         </is>
       </c>
     </row>
@@ -1083,47 +970,32 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
           <t>96,93%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>94,73; 98,83</t>
+          <t>94,92; 98,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94,97; 99,01</t>
+          <t>94,83; 98,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>95,44; 99,33</t>
+          <t>95,8; 99,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>94,49; 98,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,57; 98,38</t>
+          <t>94,79; 98,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,05; 98,89</t>
+          <t>92,4; 97,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,41; 97,77</t>
+          <t>95,61; 98,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>95,59; 98,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>95,44; 98,15</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>95,95; 98,76</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>95,17; 98,21</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,28</t>
+          <t>95,03; 98,21</t>
         </is>
       </c>
     </row>
@@ -1223,47 +1080,32 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>90,2%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
           <t>90,6%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>88,22; 91,98</t>
+          <t>88,45; 92,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,15; 90,9</t>
+          <t>86,93; 90,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88,05; 91,54</t>
+          <t>87,75; 91,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>85,37; 89,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>85,44; 89,42</t>
+          <t>89,6; 92,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>89,46; 92,82</t>
+          <t>89,47; 92,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,59; 92,99</t>
+          <t>87,52; 90,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>88,95; 91,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>87,56; 90,14</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>88,85; 91,43</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>89,26; 91,8</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,1</t>
+          <t>89,15; 91,76</t>
         </is>
       </c>
     </row>
@@ -1344,15 +1171,966 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que ven la televisión todos o casi todos los días (tasa de respuesta: 99,89%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>53743</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>82923</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>73553</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>55823</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>87574</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>77541</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>109566</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>170497</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>151094</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>45328; 61294</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>72262; 92641</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64566; 82171</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>47025; 64044</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>77840; 96764</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>69211; 86584</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>96921; 122157</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>156177; 183263</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>139047; 163178</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>733</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>693</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>246487</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>228551</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>205829</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>242468</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>266142</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>249913</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>488955</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>494693</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>455742</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>242203; 249580</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223881; 232399</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>200725; 208424</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>236725; 246991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>261940; 268306</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>244509; 253519</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>481845; 494767</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>488364; 499156</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>449227; 460593</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>125462</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>154251</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>183221</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>134689</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>155601</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>186207</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>260152</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>309852</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>369429</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>121407; 126908</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>150504; 156345</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>177934; 186375</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>129284; 138107</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>151056; 157252</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>181725; 187953</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>254321; 264196</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>304624; 312882</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>363424; 373341</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>188057</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>167156</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>170129</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>199648</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>175535</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>166554</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>387706</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>342691</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>336681</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>183542; 190906</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>162481; 169453</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166016; 172130</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>194704; 202808</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>170581; 178135</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>160823; 170135</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>381875; 392362</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>335808; 346380</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>330087; 341137</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>915</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>948</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>978</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>971</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1866</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1887</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1919</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>613750</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>632881</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>632732</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>632629</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>684852</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>680214</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1246379</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1317733</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1312946</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>601092; 625225</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>617612; 645912</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>618103; 644853</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>616993; 645702</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>672442; 697686</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>666379; 691435</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1227233; 1264402</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1299481; 1335811</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1292026; 1329840</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_dic/IP25-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP25-Edad-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,98; 58,12</t>
+          <t>42,88; 58,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,56; 63,53</t>
+          <t>49,69; 62,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49,04; 62,41</t>
+          <t>49,18; 62,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38,74; 52,76</t>
+          <t>38,86; 53,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>54,45; 67,68</t>
+          <t>54,13; 68,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,74; 69,73</t>
+          <t>55,92; 69,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,73; 53,85</t>
+          <t>42,85; 53,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>54,08; 63,46</t>
+          <t>53,92; 63,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54,35; 63,79</t>
+          <t>53,64; 63,95</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>95,65; 98,57</t>
+          <t>95,41; 98,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>94,76; 98,37</t>
+          <t>94,4; 98,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95,35; 99,01</t>
+          <t>95,53; 99,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93,29; 97,33</t>
+          <t>93,23; 97,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>97,38; 99,75</t>
+          <t>97,43; 99,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>94,75; 98,24</t>
+          <t>94,85; 98,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,05; 97,59</t>
+          <t>94,93; 97,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>96,66; 98,8</t>
+          <t>96,71; 98,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>95,87; 98,3</t>
+          <t>95,84; 98,33</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>95,19; 99,5</t>
+          <t>95,15; 99,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -908,37 +908,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>94,2; 98,66</t>
+          <t>94,31; 98,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>91,36; 97,59</t>
+          <t>91,78; 97,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>95,26; 99,17</t>
+          <t>95,44; 99,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>96,37; 99,67</t>
+          <t>96,29; 99,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,52; 98,19</t>
+          <t>94,37; 98,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>96,52; 99,13</t>
+          <t>96,58; 99,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>96,28; 98,91</t>
+          <t>96,02; 98,89</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>94,92; 98,73</t>
+          <t>94,79; 98,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94,83; 98,9</t>
+          <t>94,73; 98,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>95,8; 99,32</t>
+          <t>95,84; 99,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94,49; 98,43</t>
+          <t>94,29; 98,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,79; 98,99</t>
+          <t>94,67; 98,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,4; 97,75</t>
+          <t>92,67; 97,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,61; 98,23</t>
+          <t>95,32; 98,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>95,59; 98,6</t>
+          <t>95,76; 98,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>95,03; 98,21</t>
+          <t>94,93; 98,23</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>88,45; 92,0</t>
+          <t>88,33; 91,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>86,93; 90,92</t>
+          <t>87,07; 91,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87,75; 91,55</t>
+          <t>87,83; 91,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85,37; 89,35</t>
+          <t>85,31; 89,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>89,6; 92,97</t>
+          <t>89,36; 92,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>89,47; 92,83</t>
+          <t>89,44; 92,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,52; 90,17</t>
+          <t>87,53; 90,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>88,95; 91,44</t>
+          <t>88,91; 91,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>89,15; 91,76</t>
+          <t>89,31; 91,78</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>45328; 61294</t>
+          <t>45226; 61379</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>72262; 92641</t>
+          <t>72453; 91727</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64566; 82171</t>
+          <t>64752; 82313</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47025; 64044</t>
+          <t>47167; 65202</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>77840; 96764</t>
+          <t>77386; 97219</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69211; 86584</t>
+          <t>69430; 86831</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96921; 122157</t>
+          <t>97198; 121923</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>156177; 183263</t>
+          <t>155726; 183067</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>139047; 163178</t>
+          <t>137228; 163605</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>242203; 249580</t>
+          <t>241589; 249705</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>223881; 232399</t>
+          <t>223025; 231926</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>200725; 208424</t>
+          <t>201106; 208564</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>236725; 246991</t>
+          <t>236588; 246729</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>261940; 268306</t>
+          <t>262065; 268315</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>244509; 253519</t>
+          <t>244778; 253554</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>481845; 494767</t>
+          <t>481252; 494314</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>488364; 499156</t>
+          <t>488598; 499490</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>449227; 460593</t>
+          <t>449075; 460761</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>121407; 126908</t>
+          <t>121356; 126904</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>150504; 156345</t>
+          <t>150517; 156347</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>177934; 186375</t>
+          <t>178149; 186096</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>129284; 138107</t>
+          <t>129889; 138117</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>151056; 157252</t>
+          <t>151333; 157884</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>181725; 187953</t>
+          <t>181579; 187954</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>254321; 264196</t>
+          <t>253926; 264296</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>304624; 312882</t>
+          <t>304806; 312911</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>363424; 373341</t>
+          <t>362448; 373275</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>183542; 190906</t>
+          <t>183297; 190909</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>162481; 169453</t>
+          <t>162304; 169432</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>166016; 172130</t>
+          <t>166098; 172125</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>194704; 202808</t>
+          <t>194287; 202977</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>170581; 178135</t>
+          <t>170364; 177973</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>160823; 170135</t>
+          <t>161293; 170314</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>381875; 392362</t>
+          <t>380721; 392240</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>335808; 346380</t>
+          <t>336381; 346645</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>330087; 341137</t>
+          <t>329750; 341212</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>601092; 625225</t>
+          <t>600298; 625132</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>617612; 645912</t>
+          <t>618615; 646696</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>618103; 644853</t>
+          <t>618652; 644628</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>616993; 645702</t>
+          <t>616543; 645662</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>672442; 697686</t>
+          <t>670650; 697623</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>666379; 691435</t>
+          <t>666188; 691607</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1227233; 1264402</t>
+          <t>1227346; 1263383</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1299481; 1335811</t>
+          <t>1298862; 1337184</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1292026; 1329840</t>
+          <t>1294340; 1330065</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP25-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP25-Edad-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>45,99%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>61,26%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>62,45%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>50,96%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>56,87%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>55,87%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>45,99%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>61,26%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>62,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,88; 58,2</t>
+          <t>39,27; 53,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,69; 62,9</t>
+          <t>54,09; 67,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49,18; 62,52</t>
+          <t>55,4; 69,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38,86; 53,72</t>
+          <t>43,14; 58,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>54,13; 68,0</t>
+          <t>49,97; 62,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,92; 69,93</t>
+          <t>48,67; 62,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,85; 53,75</t>
+          <t>42,77; 53,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>53,92; 63,39</t>
+          <t>54,39; 63,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53,64; 63,95</t>
+          <t>54,13; 63,8</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>95,55%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>98,94%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>96,84%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>97,35%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>96,74%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>97,77%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>95,55%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>98,94%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>96,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>95,41; 98,62</t>
+          <t>92,92; 97,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>94,4; 98,17</t>
+          <t>97,26; 99,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95,53; 99,07</t>
+          <t>94,87; 98,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93,23; 97,23</t>
+          <t>95,3; 98,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>97,43; 99,75</t>
+          <t>94,51; 98,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>94,85; 98,25</t>
+          <t>95,39; 99,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,93; 97,51</t>
+          <t>95,03; 97,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>96,71; 98,86</t>
+          <t>96,76; 98,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>95,84; 98,33</t>
+          <t>95,85; 98,32</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>95,18%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>98,13%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>98,75%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>98,36%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>98,22%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96,99%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>95,18%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98,13%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>95,15; 99,49</t>
+          <t>91,45; 97,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>95,84; 99,56</t>
+          <t>94,52; 99,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>94,31; 98,52</t>
+          <t>96,67; 99,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>91,78; 97,6</t>
+          <t>95,12; 99,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>95,44; 99,57</t>
+          <t>95,99; 99,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>96,29; 99,67</t>
+          <t>94,21; 98,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,37; 98,23</t>
+          <t>94,73; 98,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>96,58; 99,14</t>
+          <t>96,39; 99,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>96,02; 98,89</t>
+          <t>96,24; 98,92</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>96,89%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>97,54%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>95,69%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>97,26%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>97,56%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>98,17%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>96,89%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>97,54%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>95,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>94,79; 98,73</t>
+          <t>94,57; 98,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94,73; 98,89</t>
+          <t>95,05; 98,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>95,84; 99,32</t>
+          <t>92,41; 97,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94,29; 98,51</t>
+          <t>94,73; 98,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,67; 98,9</t>
+          <t>94,97; 99,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,67; 97,85</t>
+          <t>95,44; 99,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,32; 98,2</t>
+          <t>95,44; 98,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>95,76; 98,68</t>
+          <t>95,95; 98,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>94,93; 98,23</t>
+          <t>95,17; 98,21</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>87,54%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>91,25%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>91,32%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>90,31%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>89,08%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>89,83%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>87,54%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>91,25%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>91,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>88,33; 91,99</t>
+          <t>85,44; 89,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,07; 91,03</t>
+          <t>89,46; 92,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87,83; 91,52</t>
+          <t>89,59; 92,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85,31; 89,34</t>
+          <t>88,22; 91,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>89,36; 92,96</t>
+          <t>87,15; 90,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>89,44; 92,85</t>
+          <t>88,05; 91,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,53; 90,1</t>
+          <t>87,56; 90,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>88,91; 91,53</t>
+          <t>88,85; 91,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>89,31; 91,78</t>
+          <t>89,26; 91,8</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>119</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>55823</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>87574</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>77541</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>53743</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>82923</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>73553</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>55823</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>87574</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>77541</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>45226; 61379</t>
+          <t>47670; 64567</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>72453; 91727</t>
+          <t>77330; 96740</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64752; 82313</t>
+          <t>68783; 85870</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47167; 65202</t>
+          <t>45495; 62042</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>77386; 97219</t>
+          <t>72867; 91456</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69430; 86831</t>
+          <t>64079; 81716</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97198; 121923</t>
+          <t>97009; 120881</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>155726; 183067</t>
+          <t>157056; 184591</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>137228; 163605</t>
+          <t>138482; 163207</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>368</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>328</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>325</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>368</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>242468</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>266142</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>249913</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>246487</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>228551</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>205829</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>242468</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>266142</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>249913</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>241589; 249705</t>
+          <t>235784; 246763</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>223025; 231926</t>
+          <t>261610; 268316</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>201106; 208564</t>
+          <t>244816; 253910</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>236588; 246729</t>
+          <t>241297; 249720</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>262065; 268315</t>
+          <t>223284; 231956</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>244778; 253554</t>
+          <t>200814; 208735</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>481252; 494314</t>
+          <t>481783; 494796</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>488598; 499490</t>
+          <t>488847; 499204</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>449075; 460761</t>
+          <t>449142; 460685</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>219</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>264</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>134689</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>155601</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>186207</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>125462</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>154251</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>183221</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>134689</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>155601</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>186207</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>121356; 126904</t>
+          <t>129420; 138101</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>150517; 156347</t>
+          <t>149888; 157632</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>178149; 186096</t>
+          <t>182297; 187957</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>129889; 138117</t>
+          <t>121318; 126911</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>151333; 157884</t>
+          <t>150748; 156356</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>181579; 187954</t>
+          <t>177965; 186448</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>253926; 264296</t>
+          <t>254892; 264233</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>304806; 312911</t>
+          <t>304233; 312858</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>362448; 373275</t>
+          <t>363293; 373381</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>237</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>240</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>199648</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>175535</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>166554</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>188057</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>167156</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>170129</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>199648</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>175535</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>166554</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>183297; 190909</t>
+          <t>194865; 202712</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>162304; 169432</t>
+          <t>171045; 177956</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>166098; 172125</t>
+          <t>160841; 170159</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>194287; 202977</t>
+          <t>183175; 191104</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>170364; 177973</t>
+          <t>162714; 169640</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>161293; 170314</t>
+          <t>165393; 172131</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>380721; 392240</t>
+          <t>381201; 392009</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>336381; 346645</t>
+          <t>337053; 346929</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>329750; 341212</t>
+          <t>330568; 341141</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>978</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>971</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>909</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>948</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>951</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>978</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>971</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>632629</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>684852</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>680214</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>613750</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>632881</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>632732</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>632629</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>684852</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>680214</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>600298; 625132</t>
+          <t>617477; 646203</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>618615; 646696</t>
+          <t>671348; 696627</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>618652; 644628</t>
+          <t>667283; 692635</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>616543; 645662</t>
+          <t>599517; 625109</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>670650; 697623</t>
+          <t>619167; 645775</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>666188; 691607</t>
+          <t>620191; 644772</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1227346; 1263383</t>
+          <t>1227893; 1264024</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1298862; 1337184</t>
+          <t>1298087; 1335683</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1294340; 1330065</t>
+          <t>1293630; 1330342</t>
         </is>
       </c>
     </row>
